--- a/config/BCU_GOLD.xlsx
+++ b/config/BCU_GOLD.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24111" windowHeight="11268"/>
+    <workbookView windowWidth="18519" windowHeight="11218" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="报文" sheetId="1" r:id="rId1"/>
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>35</v>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="2">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>53</v>
